--- a/dataset_agreed/saved_models/baserun/pointcloud_base_run10/epoch_80/per_file_predictions_epoch_80.xlsx
+++ b/dataset_agreed/saved_models/baserun/pointcloud_base_run10/epoch_80/per_file_predictions_epoch_80.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="500">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="497">
   <si>
     <t>Filename</t>
   </si>
@@ -808,712 +808,703 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0.9791,0.0037,0.0035,0.0008</t>
-  </si>
-  <si>
-    <t>0.0000,0.0001,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.9361,0.0006,0.0003,0.0531</t>
-  </si>
-  <si>
-    <t>0.2542,0.0001,0.0001,0.9197</t>
-  </si>
-  <si>
-    <t>0.9995,0.0002,0.0000,0.0000</t>
+    <t>0,1,0,1</t>
+  </si>
+  <si>
+    <t>0.9863,0.0041,0.0017,0.0005</t>
+  </si>
+  <si>
+    <t>0.0001,0.0003,0.0000,0.9999</t>
+  </si>
+  <si>
+    <t>0.9887,0.0001,0.0000,0.0109</t>
+  </si>
+  <si>
+    <t>0.0310,0.0000,0.0011,0.9856</t>
+  </si>
+  <si>
+    <t>0.9996,0.0002,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9992,0.0005,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9997,0.0001,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9998,0.0001,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9994,0.0003,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>1.0000,0.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9623,0.0007,0.0323,0.0003</t>
+  </si>
+  <si>
+    <t>0.1269,0.0007,0.9420,0.0000</t>
+  </si>
+  <si>
+    <t>0.0593,0.0003,0.9708,0.0000</t>
+  </si>
+  <si>
+    <t>0.0129,0.0012,0.9880,0.0002</t>
+  </si>
+  <si>
+    <t>0.9877,0.0004,0.0038,0.0007</t>
+  </si>
+  <si>
+    <t>0.0001,0.9997,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0003,0.9992,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.0024,0.9954,0.0010,0.0001</t>
+  </si>
+  <si>
+    <t>0.0003,0.9991,0.0002,0.0006</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9061,0.0006,0.0893,0.0007</t>
+  </si>
+  <si>
+    <t>0.0510,0.0006,0.9500,0.0006</t>
+  </si>
+  <si>
+    <t>0.0016,0.0001,0.9980,0.0001</t>
+  </si>
+  <si>
+    <t>0.0123,0.0007,0.9868,0.0002</t>
+  </si>
+  <si>
+    <t>0.3461,0.0001,0.7629,0.0002</t>
+  </si>
+  <si>
+    <t>0.0003,0.0000,0.9995,0.0000</t>
+  </si>
+  <si>
+    <t>0.1195,0.0000,0.9381,0.0001</t>
+  </si>
+  <si>
+    <t>0.1790,0.8426,0.0008,0.0001</t>
+  </si>
+  <si>
+    <t>0.7052,0.2814,0.0189,0.0005</t>
+  </si>
+  <si>
+    <t>0.0029,0.0021,0.9977,0.0020</t>
+  </si>
+  <si>
+    <t>0.0005,0.9990,0.0005,0.0000</t>
+  </si>
+  <si>
+    <t>0.9952,0.0007,0.0009,0.0005</t>
+  </si>
+  <si>
+    <t>0.9873,0.0008,0.0076,0.0003</t>
+  </si>
+  <si>
+    <t>0.0056,0.9923,0.0005,0.0001</t>
+  </si>
+  <si>
+    <t>0.0002,0.9964,0.1249,0.0000</t>
+  </si>
+  <si>
+    <t>0.0003,0.9987,0.0008,0.0001</t>
+  </si>
+  <si>
+    <t>0.0132,0.0037,0.9706,0.0017</t>
+  </si>
+  <si>
+    <t>0.0031,0.0108,0.9898,0.0003</t>
+  </si>
+  <si>
+    <t>0.0005,0.0000,0.9944,0.0013</t>
+  </si>
+  <si>
+    <t>0.0002,0.0105,0.9991,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.9998,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0002,0.9993,0.0076</t>
+  </si>
+  <si>
+    <t>0.0005,0.8870,0.0005,0.9751</t>
+  </si>
+  <si>
+    <t>0.0005,0.9963,0.0000,0.0020</t>
+  </si>
+  <si>
+    <t>0.0005,0.9988,0.0007,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9998,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0003,0.9999,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.0023,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0003,0.0001,0.9989,0.0003</t>
+  </si>
+  <si>
+    <t>0.0045,0.0000,0.9973,0.0000</t>
+  </si>
+  <si>
+    <t>0.0005,0.0002,0.9994,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,0.9999,0.0001</t>
+  </si>
+  <si>
+    <t>0.9980,0.0014,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9994,0.0001,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9778,0.0026,0.0165,0.0002</t>
+  </si>
+  <si>
+    <t>0.0001,0.0006,0.9999,0.0002</t>
+  </si>
+  <si>
+    <t>0.9975,0.0018,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.9753,0.0327,0.0005,0.0001</t>
+  </si>
+  <si>
+    <t>0.9987,0.0004,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.9685,0.9972,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0031,0.9998,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.0003,0.9991,0.0004</t>
+  </si>
+  <si>
+    <t>0.0000,0.9984,0.9996,0.0000</t>
+  </si>
+  <si>
+    <t>0.0005,0.0001,0.9989,0.0010</t>
+  </si>
+  <si>
+    <t>0.0050,0.9923,0.0014,0.0000</t>
+  </si>
+  <si>
+    <t>0.9772,0.0001,0.0291,0.0001</t>
+  </si>
+  <si>
+    <t>0.1264,0.0003,0.9293,0.0001</t>
+  </si>
+  <si>
+    <t>0.0003,0.0049,0.9995,0.0006</t>
+  </si>
+  <si>
+    <t>0.0000,0.9977,0.9978,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9522,0.9812,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9998,0.2999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9987,0.9910,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0000,0.0027,0.9996</t>
+  </si>
+  <si>
+    <t>0.0000,0.0003,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,0.0048,0.9998</t>
+  </si>
+  <si>
+    <t>0.0004,0.0000,0.0004,0.9996</t>
+  </si>
+  <si>
+    <t>0.0004,0.0001,0.0000,0.9997</t>
+  </si>
+  <si>
+    <t>0.0000,0.9969,0.9968,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9969,0.9982,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9922,0.9929,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9863,0.9980,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9868,0.9990,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.8360,0.9696,0.0000</t>
+  </si>
+  <si>
+    <t>0.9994,0.0004,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9992,0.0001,0.0000,0.0002</t>
+  </si>
+  <si>
+    <t>0.9974,0.0011,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9930,0.0072,0.0006,0.0001</t>
+  </si>
+  <si>
+    <t>0.9959,0.0021,0.0004,0.0003</t>
+  </si>
+  <si>
+    <t>0.9976,0.0022,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.9999,0.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9998,0.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9972,0.0021,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9976,0.0013,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.0005,0.0004,0.9993,0.0004</t>
+  </si>
+  <si>
+    <t>0.0089,0.0003,0.9918,0.0002</t>
+  </si>
+  <si>
+    <t>0.9919,0.0002,0.0015,0.0003</t>
+  </si>
+  <si>
+    <t>0.2143,0.0004,0.8649,0.0002</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0013,0.9972,0.0006,0.0001</t>
+  </si>
+  <si>
+    <t>0.0005,0.9987,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.1289,0.8798,0.0035,0.0002</t>
+  </si>
+  <si>
+    <t>0.5956,0.0050,0.3396,0.0017</t>
+  </si>
+  <si>
+    <t>0.7713,0.0004,0.2751,0.0003</t>
+  </si>
+  <si>
+    <t>0.9355,0.0046,0.0142,0.0034</t>
+  </si>
+  <si>
+    <t>0.9875,0.0013,0.0020,0.0003</t>
+  </si>
+  <si>
+    <t>0.0011,0.8752,0.0147,0.6918</t>
+  </si>
+  <si>
+    <t>0.0001,0.9996,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9997,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.9969,0.8480,0.0000</t>
+  </si>
+  <si>
+    <t>0.1538,0.8673,0.0010,0.0002</t>
+  </si>
+  <si>
+    <t>0.8950,0.1283,0.0030,0.0001</t>
+  </si>
+  <si>
+    <t>0.9971,0.0011,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9985,0.0001,0.0000,0.0007</t>
+  </si>
+  <si>
+    <t>0.9995,0.0000,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9990,0.0001,0.0001,0.0003</t>
+  </si>
+  <si>
+    <t>0.9960,0.0007,0.0011,0.0001</t>
+  </si>
+  <si>
+    <t>0.9957,0.0010,0.0004,0.0008</t>
+  </si>
+  <si>
+    <t>0.9995,0.0001,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.9347,0.9980,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.4249,0.9994,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0034,0.9994,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0001,0.9997,0.0001</t>
+  </si>
+  <si>
+    <t>0.9986,0.0000,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.8078,0.0038,0.1399,0.0034</t>
+  </si>
+  <si>
+    <t>0.3290,0.0000,0.8747,0.0000</t>
+  </si>
+  <si>
+    <t>0.9118,0.0006,0.0886,0.0008</t>
+  </si>
+  <si>
+    <t>0.0088,0.0001,0.0000,0.9984</t>
+  </si>
+  <si>
+    <t>0.0000,0.0001,0.0001,1.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9959,0.1316,0.0000</t>
+  </si>
+  <si>
+    <t>0.9981,0.0005,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.0013,0.9965,0.0005,0.0016</t>
+  </si>
+  <si>
+    <t>0.9996,0.0000,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.0779,0.9447,0.0009,0.0000</t>
+  </si>
+  <si>
+    <t>0.9995,0.0000,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.9193,0.0002,0.0044,0.0315</t>
+  </si>
+  <si>
+    <t>0.9996,0.0000,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0011,0.0012,0.9967,0.0038</t>
+  </si>
+  <si>
+    <t>0.9979,0.0000,0.0008,0.0001</t>
+  </si>
+  <si>
+    <t>0.9943,0.0001,0.0038,0.0002</t>
+  </si>
+  <si>
+    <t>0.0690,0.9213,0.0046,0.0005</t>
+  </si>
+  <si>
+    <t>0.9979,0.0002,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9664,0.0066,0.0100,0.0010</t>
+  </si>
+  <si>
+    <t>0.1517,0.0297,0.6006,0.0013</t>
+  </si>
+  <si>
+    <t>0.5980,0.0062,0.3972,0.0003</t>
+  </si>
+  <si>
+    <t>0.9826,0.0023,0.0045,0.0003</t>
+  </si>
+  <si>
+    <t>0.9967,0.0003,0.0013,0.0002</t>
+  </si>
+  <si>
+    <t>0.9995,0.0001,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9987,0.0003,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9992,0.0001,0.0002,0.0002</t>
+  </si>
+  <si>
+    <t>0.9993,0.0001,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9911,0.0039,0.0008,0.0009</t>
   </si>
   <si>
     <t>0.9996,0.0001,0.0000,0.0000</t>
   </si>
   <si>
-    <t>0.9998,0.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9999,0.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9998,0.0001,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>1.0000,0.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9495,0.0005,0.0465,0.0004</t>
-  </si>
-  <si>
-    <t>0.0077,0.0039,0.9849,0.0004</t>
-  </si>
-  <si>
-    <t>0.0123,0.0012,0.9894,0.0000</t>
-  </si>
-  <si>
-    <t>0.1519,0.0016,0.8603,0.0006</t>
-  </si>
-  <si>
-    <t>0.9410,0.0003,0.0432,0.0006</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9995,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.0426,0.9625,0.0006,0.0002</t>
-  </si>
-  <si>
-    <t>0.0001,0.9996,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.0150,0.0010,0.9768,0.0008</t>
-  </si>
-  <si>
-    <t>0.8617,0.0008,0.1747,0.0004</t>
-  </si>
-  <si>
-    <t>0.0003,0.0000,0.9995,0.0002</t>
-  </si>
-  <si>
-    <t>0.0005,0.0003,0.9986,0.0002</t>
-  </si>
-  <si>
-    <t>0.1090,0.0001,0.9390,0.0002</t>
-  </si>
-  <si>
-    <t>0.0027,0.0008,0.9926,0.0017</t>
-  </si>
-  <si>
-    <t>0.0022,0.0000,0.9987,0.0000</t>
-  </si>
-  <si>
-    <t>0.0573,0.9545,0.0007,0.0001</t>
-  </si>
-  <si>
-    <t>0.6843,0.0545,0.1782,0.0016</t>
-  </si>
-  <si>
-    <t>0.0016,0.0010,0.9987,0.0008</t>
-  </si>
-  <si>
-    <t>0.0003,0.9989,0.0014,0.0000</t>
-  </si>
-  <si>
-    <t>0.9876,0.0063,0.0012,0.0005</t>
-  </si>
-  <si>
-    <t>0.9979,0.0004,0.0004,0.0001</t>
-  </si>
-  <si>
-    <t>0.0541,0.9499,0.0015,0.0001</t>
-  </si>
-  <si>
-    <t>0.0002,0.9844,0.7507,0.0000</t>
-  </si>
-  <si>
-    <t>0.0074,0.7903,0.1788,0.0020</t>
-  </si>
-  <si>
-    <t>0.0042,0.0013,0.9874,0.0014</t>
-  </si>
-  <si>
-    <t>0.0021,0.0072,0.9921,0.0002</t>
-  </si>
-  <si>
-    <t>0.0081,0.0000,0.9756,0.0009</t>
-  </si>
-  <si>
-    <t>0.0014,0.0063,0.9975,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0003,0.9996,0.0026</t>
-  </si>
-  <si>
-    <t>0.0035,0.3783,0.0002,0.9691</t>
-  </si>
-  <si>
-    <t>0.0062,0.9573,0.0000,0.0011</t>
-  </si>
-  <si>
-    <t>0.0005,0.9986,0.0009,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9995,0.0003,0.0000</t>
+    <t>0.9986,0.0000,0.0003,0.0003</t>
+  </si>
+  <si>
+    <t>0.9621,0.0223,0.0002,0.0007</t>
+  </si>
+  <si>
+    <t>0.7959,0.2963,0.0004,0.0000</t>
+  </si>
+  <si>
+    <t>0.9836,0.0137,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.1074,0.0004,0.9136,0.0015</t>
+  </si>
+  <si>
+    <t>0.9933,0.0062,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.9959,0.0007,0.0006,0.0011</t>
+  </si>
+  <si>
+    <t>0.9956,0.0019,0.0010,0.0001</t>
+  </si>
+  <si>
+    <t>0.9645,0.0046,0.0187,0.0008</t>
+  </si>
+  <si>
+    <t>0.0003,0.0001,0.9998,0.0000</t>
+  </si>
+  <si>
+    <t>0.9344,0.0218,0.0266,0.0004</t>
   </si>
   <si>
     <t>0.0000,0.0000,1.0000,0.0000</t>
   </si>
   <si>
-    <t>0.0004,0.1973,0.9937,0.0001</t>
-  </si>
-  <si>
-    <t>0.0023,0.0003,0.9957,0.0006</t>
-  </si>
-  <si>
-    <t>0.0014,0.0000,0.9990,0.0000</t>
-  </si>
-  <si>
-    <t>0.0011,0.0002,0.9978,0.0005</t>
-  </si>
-  <si>
-    <t>0.0000,0.0001,0.9999,0.0001</t>
-  </si>
-  <si>
-    <t>0.9960,0.0024,0.0003,0.0002</t>
-  </si>
-  <si>
-    <t>0.9987,0.0003,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.9971,0.0009,0.0011,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.0024,0.9999,0.0001</t>
-  </si>
-  <si>
-    <t>0.9978,0.0014,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9803,0.0260,0.0004,0.0000</t>
-  </si>
-  <si>
-    <t>0.9995,0.0001,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9906,0.9958,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0005,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0003,0.9997,0.0002</t>
-  </si>
-  <si>
-    <t>0.0000,0.9988,0.9995,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0000,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0050,0.9939,0.0006,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9998,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9809,0.0003,0.0188,0.0001</t>
-  </si>
-  <si>
-    <t>0.0706,0.0010,0.9543,0.0002</t>
-  </si>
-  <si>
-    <t>0.0003,0.0089,0.9993,0.0007</t>
-  </si>
-  <si>
-    <t>0.0000,0.9989,0.9946,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9423,0.9919,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.7469,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9979,0.1039,0.0000</t>
-  </si>
-  <si>
-    <t>0.0010,0.0001,0.0032,0.9985</t>
-  </si>
-  <si>
-    <t>0.0000,0.0002,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0000,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,0.0009,0.9998</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,0.0007,0.9999</t>
-  </si>
-  <si>
-    <t>0.0001,0.0001,0.0001,0.9999</t>
-  </si>
-  <si>
-    <t>0.0000,0.9992,0.9902,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9928,0.9885,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9983,0.8666,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9988,0.9997,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9985,0.7797,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9990,0.7477,0.0000</t>
-  </si>
-  <si>
-    <t>0.9999,0.0001,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9989,0.0010,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9992,0.0001,0.0000,0.0002</t>
-  </si>
-  <si>
-    <t>0.9933,0.0044,0.0003,0.0002</t>
-  </si>
-  <si>
-    <t>0.9957,0.0035,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9966,0.0018,0.0003,0.0002</t>
-  </si>
-  <si>
-    <t>0.9990,0.0011,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9993,0.0003,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9994,0.0002,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9995,0.0001,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9978,0.0017,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9984,0.0004,0.0002,0.0002</t>
-  </si>
-  <si>
-    <t>0.0028,0.0001,0.9987,0.0001</t>
-  </si>
-  <si>
-    <t>0.0022,0.0003,0.9973,0.0001</t>
-  </si>
-  <si>
-    <t>0.9884,0.0002,0.0029,0.0006</t>
-  </si>
-  <si>
-    <t>0.1208,0.0002,0.9132,0.0002</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0013,0.9971,0.0015,0.0000</t>
-  </si>
-  <si>
-    <t>0.0031,0.9953,0.0004,0.0001</t>
-  </si>
-  <si>
-    <t>0.6026,0.4250,0.0066,0.0002</t>
-  </si>
-  <si>
-    <t>0.6723,0.0005,0.3092,0.0013</t>
-  </si>
-  <si>
-    <t>0.9756,0.0001,0.0320,0.0001</t>
-  </si>
-  <si>
-    <t>0.6638,0.0261,0.2035,0.0026</t>
-  </si>
-  <si>
-    <t>0.7991,0.0055,0.1266,0.0031</t>
-  </si>
-  <si>
-    <t>0.0018,0.1636,0.0004,0.9899</t>
-  </si>
-  <si>
-    <t>0.0007,0.9980,0.0016,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.9997,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9913,0.9847,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9999,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.3822,0.6997,0.0005,0.0000</t>
-  </si>
-  <si>
-    <t>0.8458,0.1516,0.0022,0.0004</t>
-  </si>
-  <si>
-    <t>0.9987,0.0006,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9996,0.0000,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9990,0.0002,0.0001,0.0003</t>
-  </si>
-  <si>
-    <t>0.9996,0.0000,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9982,0.0004,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.9952,0.0010,0.0003,0.0010</t>
-  </si>
-  <si>
-    <t>0.9992,0.0001,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.0002,0.4962,0.9931,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.8305,0.9989,0.0000</t>
-  </si>
-  <si>
-    <t>0.0005,0.0028,0.9985,0.0000</t>
-  </si>
-  <si>
-    <t>0.0050,0.0025,0.9850,0.0009</t>
-  </si>
-  <si>
-    <t>0.9965,0.0003,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.0700,0.0032,0.9192,0.0010</t>
-  </si>
-  <si>
-    <t>0.2461,0.0002,0.8630,0.0001</t>
-  </si>
-  <si>
-    <t>0.9871,0.0002,0.0059,0.0003</t>
-  </si>
-  <si>
-    <t>0.0057,0.0000,0.0000,0.9990</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,0.0001,1.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0000,0.0001,0.9999</t>
-  </si>
-  <si>
-    <t>0.0000,0.9984,0.1759,0.0000</t>
-  </si>
-  <si>
-    <t>0.9993,0.0001,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.0010,0.9979,0.0003,0.0005</t>
-  </si>
-  <si>
-    <t>0.6612,0.4431,0.0005,0.0000</t>
-  </si>
-  <si>
-    <t>0.9968,0.0002,0.0016,0.0001</t>
-  </si>
-  <si>
-    <t>0.8655,0.0002,0.0005,0.1135</t>
-  </si>
-  <si>
-    <t>0.0027,0.0047,0.9919,0.0065</t>
-  </si>
-  <si>
-    <t>0.9983,0.0000,0.0008,0.0001</t>
-  </si>
-  <si>
-    <t>0.9988,0.0001,0.0004,0.0001</t>
-  </si>
-  <si>
-    <t>0.1121,0.6117,0.0895,0.0005</t>
-  </si>
-  <si>
-    <t>0.9970,0.0003,0.0002,0.0002</t>
-  </si>
-  <si>
-    <t>0.9949,0.0010,0.0005,0.0003</t>
-  </si>
-  <si>
-    <t>0.3283,0.0503,0.2267,0.0034</t>
-  </si>
-  <si>
-    <t>0.9852,0.0022,0.0035,0.0001</t>
-  </si>
-  <si>
-    <t>0.9950,0.0010,0.0005,0.0001</t>
-  </si>
-  <si>
-    <t>0.9965,0.0009,0.0009,0.0002</t>
-  </si>
-  <si>
-    <t>0.9997,0.0001,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9987,0.0002,0.0002,0.0002</t>
-  </si>
-  <si>
-    <t>0.9986,0.0001,0.0005,0.0003</t>
-  </si>
-  <si>
-    <t>0.9920,0.0007,0.0017,0.0023</t>
-  </si>
-  <si>
-    <t>0.9995,0.0001,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9995,0.0000,0.0000,0.0002</t>
-  </si>
-  <si>
-    <t>0.9631,0.0307,0.0002,0.0003</t>
-  </si>
-  <si>
-    <t>0.8967,0.1164,0.0017,0.0001</t>
-  </si>
-  <si>
-    <t>0.8965,0.1055,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9306,0.0154,0.0252,0.0015</t>
-  </si>
-  <si>
-    <t>0.9910,0.0093,0.0006,0.0001</t>
-  </si>
-  <si>
-    <t>0.9984,0.0002,0.0001,0.0005</t>
-  </si>
-  <si>
-    <t>0.9966,0.0015,0.0006,0.0001</t>
-  </si>
-  <si>
-    <t>0.9362,0.0319,0.0173,0.0008</t>
-  </si>
-  <si>
-    <t>0.0005,0.0007,0.9998,0.0000</t>
-  </si>
-  <si>
-    <t>0.9933,0.0032,0.0014,0.0002</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0021,0.0037,0.9901,0.0024</t>
-  </si>
-  <si>
-    <t>0.0001,0.0001,0.9998,0.0000</t>
-  </si>
-  <si>
-    <t>0.0009,0.0988,0.9849,0.0002</t>
-  </si>
-  <si>
-    <t>0.0001,0.0020,0.9998,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0002,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0188,0.0023,0.9702,0.0010</t>
-  </si>
-  <si>
-    <t>0.0172,0.0017,0.9792,0.0004</t>
-  </si>
-  <si>
-    <t>0.0013,0.0068,0.9952,0.0002</t>
-  </si>
-  <si>
-    <t>0.0297,0.1526,0.8091,0.0001</t>
-  </si>
-  <si>
-    <t>0.0143,0.0196,0.9614,0.0003</t>
-  </si>
-  <si>
-    <t>0.9387,0.0055,0.0348,0.0003</t>
-  </si>
-  <si>
-    <t>0.8815,0.0033,0.0705,0.0031</t>
-  </si>
-  <si>
-    <t>0.0348,0.0015,0.9656,0.0002</t>
-  </si>
-  <si>
-    <t>0.0014,0.9979,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.0006,0.9990,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.9297,0.1037,0.0005,0.0000</t>
-  </si>
-  <si>
-    <t>0.1662,0.8871,0.0009,0.0000</t>
-  </si>
-  <si>
-    <t>0.0224,0.9788,0.0004,0.0001</t>
-  </si>
-  <si>
-    <t>0.7932,0.0781,0.0020,0.0013</t>
-  </si>
-  <si>
-    <t>0.7246,0.0004,0.2548,0.0015</t>
-  </si>
-  <si>
-    <t>0.8985,0.0020,0.0043,0.0237</t>
-  </si>
-  <si>
-    <t>0.7563,0.0052,0.1698,0.0058</t>
-  </si>
-  <si>
-    <t>0.9533,0.0013,0.0323,0.0007</t>
-  </si>
-  <si>
-    <t>0.0006,0.0005,0.9991,0.0002</t>
-  </si>
-  <si>
-    <t>0.0014,0.0049,0.9859,0.0020</t>
-  </si>
-  <si>
-    <t>0.0063,0.0043,0.9815,0.0011</t>
-  </si>
-  <si>
-    <t>0.0027,0.0003,0.9957,0.0002</t>
-  </si>
-  <si>
-    <t>0.0003,0.4011,0.9191,0.0009</t>
-  </si>
-  <si>
-    <t>0.9973,0.0008,0.0003,0.0004</t>
-  </si>
-  <si>
-    <t>0.9941,0.0029,0.0004,0.0006</t>
-  </si>
-  <si>
-    <t>0.9980,0.0014,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9959,0.0027,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9976,0.0012,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9982,0.0011,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9996,0.0000,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.0002,0.0003,0.9994,0.0007</t>
-  </si>
-  <si>
-    <t>0.0053,0.0097,0.9762,0.0030</t>
-  </si>
-  <si>
-    <t>0.8676,0.0043,0.0440,0.0104</t>
-  </si>
-  <si>
-    <t>0.0006,0.0009,0.9991,0.0000</t>
-  </si>
-  <si>
-    <t>0.0004,0.0013,0.9991,0.0001</t>
-  </si>
-  <si>
-    <t>0.0018,0.0991,0.9792,0.0008</t>
-  </si>
-  <si>
-    <t>0.0024,0.0000,0.9996,0.0000</t>
-  </si>
-  <si>
-    <t>0.9262,0.0011,0.0711,0.0006</t>
-  </si>
-  <si>
-    <t>0.0001,0.0001,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0003,0.0004,0.9988,0.0005</t>
-  </si>
-  <si>
-    <t>0.0646,0.0200,0.8509,0.0044</t>
-  </si>
-  <si>
-    <t>0.9760,0.0007,0.0098,0.0008</t>
-  </si>
-  <si>
-    <t>0.9480,0.0011,0.0298,0.0014</t>
-  </si>
-  <si>
-    <t>0.9783,0.0008,0.0098,0.0002</t>
-  </si>
-  <si>
-    <t>0.9990,0.0003,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9879,0.0151,0.0004,0.0000</t>
-  </si>
-  <si>
-    <t>0.9918,0.0098,0.0004,0.0000</t>
-  </si>
-  <si>
-    <t>0.9993,0.0001,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.9983,0.0011,0.0001,0.0000</t>
+    <t>0.0016,0.0031,0.9935,0.0019</t>
+  </si>
+  <si>
+    <t>0.0001,0.0003,0.9998,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.0219,0.9986,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.0004,0.9998,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0003,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0053,0.0008,0.9907,0.0002</t>
+  </si>
+  <si>
+    <t>0.8475,0.0043,0.1320,0.0008</t>
+  </si>
+  <si>
+    <t>0.0220,0.0069,0.9640,0.0004</t>
+  </si>
+  <si>
+    <t>0.0509,0.0050,0.9348,0.0003</t>
+  </si>
+  <si>
+    <t>0.0371,0.0165,0.9209,0.0002</t>
+  </si>
+  <si>
+    <t>0.6372,0.0039,0.4643,0.0003</t>
+  </si>
+  <si>
+    <t>0.8968,0.0054,0.0369,0.0052</t>
+  </si>
+  <si>
+    <t>0.2868,0.0013,0.7660,0.0005</t>
+  </si>
+  <si>
+    <t>0.0080,0.9901,0.0009,0.0000</t>
+  </si>
+  <si>
+    <t>0.7146,0.3907,0.0006,0.0000</t>
+  </si>
+  <si>
+    <t>0.0921,0.9234,0.0011,0.0001</t>
+  </si>
+  <si>
+    <t>0.0053,0.9934,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.9834,0.0007,0.0055,0.0002</t>
+  </si>
+  <si>
+    <t>0.8747,0.0001,0.1332,0.0008</t>
+  </si>
+  <si>
+    <t>0.9861,0.0005,0.0008,0.0013</t>
+  </si>
+  <si>
+    <t>0.6137,0.0103,0.3049,0.0091</t>
+  </si>
+  <si>
+    <t>0.0351,0.0015,0.9552,0.0019</t>
+  </si>
+  <si>
+    <t>0.0017,0.0006,0.9978,0.0002</t>
+  </si>
+  <si>
+    <t>0.0009,0.0009,0.9962,0.0003</t>
+  </si>
+  <si>
+    <t>0.0062,0.0046,0.9817,0.0010</t>
+  </si>
+  <si>
+    <t>0.0020,0.0013,0.9952,0.0001</t>
+  </si>
+  <si>
+    <t>0.0002,0.0027,0.9977,0.0005</t>
+  </si>
+  <si>
+    <t>0.9985,0.0001,0.0000,0.0004</t>
+  </si>
+  <si>
+    <t>0.9850,0.0167,0.0011,0.0003</t>
+  </si>
+  <si>
+    <t>0.9883,0.0033,0.0017,0.0037</t>
+  </si>
+  <si>
+    <t>0.9989,0.0007,0.0001,0.0000</t>
   </si>
   <si>
     <t>0.9974,0.0014,0.0002,0.0001</t>
   </si>
   <si>
-    <t>0.9997,0.0001,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.0008,0.0198,0.9958,0.0001</t>
-  </si>
-  <si>
-    <t>0.0011,0.0025,0.9968,0.0002</t>
-  </si>
-  <si>
-    <t>0.0001,0.1164,0.9985,0.0001</t>
-  </si>
-  <si>
-    <t>0.0112,0.1079,0.8338,0.0023</t>
-  </si>
-  <si>
-    <t>0.0001,0.0001,0.9998,0.0001</t>
-  </si>
-  <si>
-    <t>0.0117,0.0006,0.5494,0.1197</t>
-  </si>
-  <si>
-    <t>0.0066,0.0019,0.9891,0.0004</t>
-  </si>
-  <si>
-    <t>0.0025,0.0004,0.9920,0.0025</t>
-  </si>
-  <si>
-    <t>0.9534,0.0001,0.0044,0.0197</t>
-  </si>
-  <si>
-    <t>0.0003,0.0012,0.0000,0.9998</t>
-  </si>
-  <si>
-    <t>0.0029,0.0000,0.0000,0.9997</t>
-  </si>
-  <si>
-    <t>0.9954,0.0002,0.0001,0.0008</t>
+    <t>0.9993,0.0004,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9982,0.0006,0.0002,0.0003</t>
+  </si>
+  <si>
+    <t>0.9988,0.0004,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.0006,0.0004,0.9987,0.0008</t>
+  </si>
+  <si>
+    <t>0.0037,0.0243,0.9728,0.0015</t>
+  </si>
+  <si>
+    <t>0.8841,0.0005,0.0501,0.0056</t>
+  </si>
+  <si>
+    <t>0.0035,0.0016,0.9967,0.0001</t>
+  </si>
+  <si>
+    <t>0.0002,0.0003,0.9998,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.8774,0.9819,0.0001</t>
+  </si>
+  <si>
+    <t>0.0004,0.0001,0.9992,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.0001,1.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0004,0.0006,0.9988,0.0003</t>
+  </si>
+  <si>
+    <t>0.0005,0.0035,0.9972,0.0005</t>
+  </si>
+  <si>
+    <t>0.9743,0.0027,0.0072,0.0003</t>
+  </si>
+  <si>
+    <t>0.9280,0.0008,0.0582,0.0010</t>
+  </si>
+  <si>
+    <t>0.9921,0.0002,0.0023,0.0001</t>
+  </si>
+  <si>
+    <t>0.9972,0.0014,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9934,0.0055,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.9969,0.0029,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9986,0.0011,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9971,0.0015,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9985,0.0004,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.0022,0.0036,0.9939,0.0002</t>
+  </si>
+  <si>
+    <t>0.0036,0.0059,0.9895,0.0006</t>
+  </si>
+  <si>
+    <t>0.0000,0.9979,0.9527,0.0000</t>
+  </si>
+  <si>
+    <t>0.0057,0.0017,0.9876,0.0012</t>
+  </si>
+  <si>
+    <t>0.0024,0.0001,0.9983,0.0001</t>
+  </si>
+  <si>
+    <t>0.0047,0.0002,0.9868,0.0024</t>
+  </si>
+  <si>
+    <t>0.0136,0.0008,0.9839,0.0004</t>
+  </si>
+  <si>
+    <t>0.0060,0.0008,0.9835,0.0044</t>
+  </si>
+  <si>
+    <t>0.9034,0.0001,0.0149,0.0257</t>
+  </si>
+  <si>
+    <t>0.0004,0.0011,0.0000,0.9998</t>
+  </si>
+  <si>
+    <t>0.0341,0.0000,0.0000,0.9974</t>
+  </si>
+  <si>
+    <t>0.9979,0.0001,0.0001,0.0002</t>
   </si>
 </sst>
 </file>
@@ -1899,7 +1890,7 @@
         <v>259</v>
       </c>
       <c r="D2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1913,7 +1904,7 @@
         <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1927,7 +1918,7 @@
         <v>259</v>
       </c>
       <c r="D4" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1941,7 +1932,7 @@
         <v>260</v>
       </c>
       <c r="D5" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -1955,7 +1946,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -1969,7 +1960,7 @@
         <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -1983,7 +1974,7 @@
         <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -1997,7 +1988,7 @@
         <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2011,7 +2002,7 @@
         <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2025,7 +2016,7 @@
         <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2039,7 +2030,7 @@
         <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2053,7 +2044,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2067,7 +2058,7 @@
         <v>259</v>
       </c>
       <c r="D14" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2081,7 +2072,7 @@
         <v>261</v>
       </c>
       <c r="D15" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2095,7 +2086,7 @@
         <v>261</v>
       </c>
       <c r="D16" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2109,7 +2100,7 @@
         <v>261</v>
       </c>
       <c r="D17" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2123,7 +2114,7 @@
         <v>259</v>
       </c>
       <c r="D18" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2137,7 +2128,7 @@
         <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2151,7 +2142,7 @@
         <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2165,7 +2156,7 @@
         <v>262</v>
       </c>
       <c r="D21" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2179,7 +2170,7 @@
         <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2193,7 +2184,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>279</v>
+        <v>284</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2204,10 +2195,10 @@
         <v>259</v>
       </c>
       <c r="C24" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D24" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2218,10 +2209,10 @@
         <v>259</v>
       </c>
       <c r="C25" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D25" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2235,7 +2226,7 @@
         <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2249,7 +2240,7 @@
         <v>261</v>
       </c>
       <c r="D27" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2263,7 +2254,7 @@
         <v>261</v>
       </c>
       <c r="D28" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2277,7 +2268,7 @@
         <v>261</v>
       </c>
       <c r="D29" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2291,7 +2282,7 @@
         <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2305,7 +2296,7 @@
         <v>262</v>
       </c>
       <c r="D31" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2319,7 +2310,7 @@
         <v>259</v>
       </c>
       <c r="D32" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2333,7 +2324,7 @@
         <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2347,7 +2338,7 @@
         <v>262</v>
       </c>
       <c r="D34" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2361,7 +2352,7 @@
         <v>259</v>
       </c>
       <c r="D35" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2375,7 +2366,7 @@
         <v>259</v>
       </c>
       <c r="D36" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2389,7 +2380,7 @@
         <v>262</v>
       </c>
       <c r="D37" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2400,10 +2391,10 @@
         <v>262</v>
       </c>
       <c r="C38" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D38" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2417,7 +2408,7 @@
         <v>262</v>
       </c>
       <c r="D39" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2431,7 +2422,7 @@
         <v>261</v>
       </c>
       <c r="D40" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2445,7 +2436,7 @@
         <v>261</v>
       </c>
       <c r="D41" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2459,7 +2450,7 @@
         <v>261</v>
       </c>
       <c r="D42" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2473,7 +2464,7 @@
         <v>261</v>
       </c>
       <c r="D43" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2487,7 +2478,7 @@
         <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2501,7 +2492,7 @@
         <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2512,10 +2503,10 @@
         <v>259</v>
       </c>
       <c r="C46" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="D46" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2529,7 +2520,7 @@
         <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2543,7 +2534,7 @@
         <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2557,7 +2548,7 @@
         <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2571,7 +2562,7 @@
         <v>261</v>
       </c>
       <c r="D50" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2585,7 +2576,7 @@
         <v>261</v>
       </c>
       <c r="D51" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2599,7 +2590,7 @@
         <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2613,7 +2604,7 @@
         <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2627,7 +2618,7 @@
         <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2641,7 +2632,7 @@
         <v>261</v>
       </c>
       <c r="D55" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2655,7 +2646,7 @@
         <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2669,7 +2660,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2683,7 +2674,7 @@
         <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2697,7 +2688,7 @@
         <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2711,7 +2702,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2725,7 +2716,7 @@
         <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2739,7 +2730,7 @@
         <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2753,7 +2744,7 @@
         <v>263</v>
       </c>
       <c r="D63" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2767,7 +2758,7 @@
         <v>261</v>
       </c>
       <c r="D64" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2781,7 +2772,7 @@
         <v>261</v>
       </c>
       <c r="D65" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2795,7 +2786,7 @@
         <v>263</v>
       </c>
       <c r="D66" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2809,7 +2800,7 @@
         <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2823,7 +2814,7 @@
         <v>262</v>
       </c>
       <c r="D68" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2837,7 +2828,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>328</v>
+        <v>310</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2851,7 +2842,7 @@
         <v>259</v>
       </c>
       <c r="D70" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2865,7 +2856,7 @@
         <v>261</v>
       </c>
       <c r="D71" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2879,7 +2870,7 @@
         <v>261</v>
       </c>
       <c r="D72" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2893,7 +2884,7 @@
         <v>263</v>
       </c>
       <c r="D73" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2907,7 +2898,7 @@
         <v>263</v>
       </c>
       <c r="D74" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2918,10 +2909,10 @@
         <v>262</v>
       </c>
       <c r="C75" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D75" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2932,10 +2923,10 @@
         <v>262</v>
       </c>
       <c r="C76" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D76" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -2949,7 +2940,7 @@
         <v>260</v>
       </c>
       <c r="D77" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -2963,7 +2954,7 @@
         <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -2977,7 +2968,7 @@
         <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -2991,7 +2982,7 @@
         <v>260</v>
       </c>
       <c r="D80" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -3005,7 +2996,7 @@
         <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -3019,7 +3010,7 @@
         <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3033,7 +3024,7 @@
         <v>263</v>
       </c>
       <c r="D83" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3047,7 +3038,7 @@
         <v>263</v>
       </c>
       <c r="D84" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3061,7 +3052,7 @@
         <v>263</v>
       </c>
       <c r="D85" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3075,7 +3066,7 @@
         <v>263</v>
       </c>
       <c r="D86" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3089,7 +3080,7 @@
         <v>263</v>
       </c>
       <c r="D87" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3103,7 +3094,7 @@
         <v>263</v>
       </c>
       <c r="D88" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3117,7 +3108,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3131,7 +3122,7 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>348</v>
+        <v>272</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3229,7 +3220,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>271</v>
+        <v>355</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3243,7 +3234,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3257,7 +3248,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>356</v>
+        <v>274</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3271,7 +3262,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3285,7 +3276,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3299,7 +3290,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3313,7 +3304,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3327,7 +3318,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>272</v>
+        <v>356</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3341,7 +3332,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3355,7 +3346,7 @@
         <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3369,7 +3360,7 @@
         <v>259</v>
       </c>
       <c r="D107" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3383,7 +3374,7 @@
         <v>261</v>
       </c>
       <c r="D108" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3397,7 +3388,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>279</v>
+        <v>284</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3411,7 +3402,7 @@
         <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3425,7 +3416,7 @@
         <v>262</v>
       </c>
       <c r="D111" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3439,7 +3430,7 @@
         <v>262</v>
       </c>
       <c r="D112" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3453,7 +3444,7 @@
         <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3467,7 +3458,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3478,7 +3469,7 @@
         <v>262</v>
       </c>
       <c r="C115" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D115" t="s">
         <v>367</v>
@@ -3548,7 +3539,7 @@
         <v>262</v>
       </c>
       <c r="C120" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="D120" t="s">
         <v>372</v>
@@ -3593,7 +3584,7 @@
         <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>375</v>
+        <v>284</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3607,7 +3598,7 @@
         <v>263</v>
       </c>
       <c r="D124" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3621,7 +3612,7 @@
         <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>377</v>
+        <v>366</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3635,7 +3626,7 @@
         <v>262</v>
       </c>
       <c r="D126" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3649,7 +3640,7 @@
         <v>259</v>
       </c>
       <c r="D127" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3663,7 +3654,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3677,7 +3668,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>381</v>
+        <v>318</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3691,7 +3682,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3705,7 +3696,7 @@
         <v>259</v>
       </c>
       <c r="D131" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3719,7 +3710,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>271</v>
+        <v>381</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3733,7 +3724,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3747,7 +3738,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3761,7 +3752,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3772,10 +3763,10 @@
         <v>263</v>
       </c>
       <c r="C136" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D136" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3786,10 +3777,10 @@
         <v>261</v>
       </c>
       <c r="C137" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D137" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3803,7 +3794,7 @@
         <v>261</v>
       </c>
       <c r="D138" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3817,7 +3808,7 @@
         <v>261</v>
       </c>
       <c r="D139" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3831,7 +3822,7 @@
         <v>259</v>
       </c>
       <c r="D140" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3842,10 +3833,10 @@
         <v>259</v>
       </c>
       <c r="C141" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D141" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3859,7 +3850,7 @@
         <v>261</v>
       </c>
       <c r="D142" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3873,7 +3864,7 @@
         <v>259</v>
       </c>
       <c r="D143" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3887,7 +3878,7 @@
         <v>260</v>
       </c>
       <c r="D144" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3901,7 +3892,7 @@
         <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>396</v>
+        <v>339</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3915,7 +3906,7 @@
         <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3929,7 +3920,7 @@
         <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>398</v>
+        <v>339</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -3943,7 +3934,7 @@
         <v>262</v>
       </c>
       <c r="D148" t="s">
-        <v>399</v>
+        <v>395</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -3957,7 +3948,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>400</v>
+        <v>396</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -3971,7 +3962,7 @@
         <v>262</v>
       </c>
       <c r="D150" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -3985,7 +3976,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>271</v>
+        <v>398</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -3996,10 +3987,10 @@
         <v>262</v>
       </c>
       <c r="C152" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D152" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -4013,7 +4004,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4027,7 +4018,7 @@
         <v>259</v>
       </c>
       <c r="D154" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4041,7 +4032,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>271</v>
+        <v>402</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4055,7 +4046,7 @@
         <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4069,7 +4060,7 @@
         <v>259</v>
       </c>
       <c r="D157" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4083,7 +4074,7 @@
         <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4097,7 +4088,7 @@
         <v>262</v>
       </c>
       <c r="D159" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4111,7 +4102,7 @@
         <v>259</v>
       </c>
       <c r="D160" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4125,7 +4116,7 @@
         <v>259</v>
       </c>
       <c r="D161" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4136,10 +4127,10 @@
         <v>262</v>
       </c>
       <c r="C162" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D162" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4153,7 +4144,7 @@
         <v>259</v>
       </c>
       <c r="D163" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4167,7 +4158,7 @@
         <v>259</v>
       </c>
       <c r="D164" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4181,7 +4172,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4195,7 +4186,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4209,7 +4200,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4223,7 +4214,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4237,7 +4228,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>357</v>
+        <v>416</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4251,7 +4242,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4265,7 +4256,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4279,7 +4270,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4293,7 +4284,7 @@
         <v>259</v>
       </c>
       <c r="D173" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4307,7 +4298,7 @@
         <v>259</v>
       </c>
       <c r="D174" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4321,7 +4312,7 @@
         <v>259</v>
       </c>
       <c r="D175" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4332,10 +4323,10 @@
         <v>261</v>
       </c>
       <c r="C176" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D176" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4349,7 +4340,7 @@
         <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4363,7 +4354,7 @@
         <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4377,7 +4368,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4391,7 +4382,7 @@
         <v>259</v>
       </c>
       <c r="D180" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4405,7 +4396,7 @@
         <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4419,7 +4410,7 @@
         <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4433,7 +4424,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4447,7 +4438,7 @@
         <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4461,7 +4452,7 @@
         <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4475,7 +4466,7 @@
         <v>261</v>
       </c>
       <c r="D186" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4489,7 +4480,7 @@
         <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4503,7 +4494,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>326</v>
+        <v>430</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4517,7 +4508,7 @@
         <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4531,7 +4522,7 @@
         <v>261</v>
       </c>
       <c r="D190" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4542,10 +4533,10 @@
         <v>259</v>
       </c>
       <c r="C191" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D191" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4559,7 +4550,7 @@
         <v>261</v>
       </c>
       <c r="D192" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4573,7 +4564,7 @@
         <v>261</v>
       </c>
       <c r="D193" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4587,7 +4578,7 @@
         <v>261</v>
       </c>
       <c r="D194" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4601,7 +4592,7 @@
         <v>259</v>
       </c>
       <c r="D195" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4615,7 +4606,7 @@
         <v>259</v>
       </c>
       <c r="D196" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4629,7 +4620,7 @@
         <v>261</v>
       </c>
       <c r="D197" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4643,7 +4634,7 @@
         <v>262</v>
       </c>
       <c r="D198" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4657,7 +4648,7 @@
         <v>262</v>
       </c>
       <c r="D199" t="s">
-        <v>446</v>
+        <v>310</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4671,7 +4662,7 @@
         <v>259</v>
       </c>
       <c r="D200" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4685,7 +4676,7 @@
         <v>262</v>
       </c>
       <c r="D201" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4699,7 +4690,7 @@
         <v>262</v>
       </c>
       <c r="D202" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4713,7 +4704,7 @@
         <v>259</v>
       </c>
       <c r="D203" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4727,7 +4718,7 @@
         <v>259</v>
       </c>
       <c r="D204" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4741,7 +4732,7 @@
         <v>259</v>
       </c>
       <c r="D205" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4755,7 +4746,7 @@
         <v>259</v>
       </c>
       <c r="D206" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4766,10 +4757,10 @@
         <v>259</v>
       </c>
       <c r="C207" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D207" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4783,7 +4774,7 @@
         <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4797,7 +4788,7 @@
         <v>261</v>
       </c>
       <c r="D209" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4811,7 +4802,7 @@
         <v>261</v>
       </c>
       <c r="D210" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4825,7 +4816,7 @@
         <v>261</v>
       </c>
       <c r="D211" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4839,7 +4830,7 @@
         <v>261</v>
       </c>
       <c r="D212" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4853,7 +4844,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>350</v>
+        <v>458</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4867,7 +4858,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4881,7 +4872,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4895,7 +4886,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4909,7 +4900,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4923,7 +4914,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4937,7 +4928,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -4951,7 +4942,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -4965,7 +4956,7 @@
         <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -4979,7 +4970,7 @@
         <v>261</v>
       </c>
       <c r="D222" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -4993,7 +4984,7 @@
         <v>259</v>
       </c>
       <c r="D223" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -5007,7 +4998,7 @@
         <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5021,7 +5012,7 @@
         <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5032,10 +5023,10 @@
         <v>261</v>
       </c>
       <c r="C226" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D226" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5049,7 +5040,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>473</v>
+        <v>430</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5060,10 +5051,10 @@
         <v>261</v>
       </c>
       <c r="C228" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D228" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5077,7 +5068,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5091,7 +5082,7 @@
         <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5105,7 +5096,7 @@
         <v>261</v>
       </c>
       <c r="D231" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5119,7 +5110,7 @@
         <v>259</v>
       </c>
       <c r="D232" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5133,7 +5124,7 @@
         <v>259</v>
       </c>
       <c r="D233" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5147,7 +5138,7 @@
         <v>259</v>
       </c>
       <c r="D234" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5161,7 +5152,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5175,7 +5166,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5189,7 +5180,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>271</v>
+        <v>355</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5203,7 +5194,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5217,7 +5208,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>484</v>
+        <v>418</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5231,7 +5222,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5245,7 +5236,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>486</v>
+        <v>483</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5259,7 +5250,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5273,7 +5264,7 @@
         <v>261</v>
       </c>
       <c r="D243" t="s">
-        <v>488</v>
+        <v>485</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5287,7 +5278,7 @@
         <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5298,10 +5289,10 @@
         <v>261</v>
       </c>
       <c r="C245" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D245" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5315,7 +5306,7 @@
         <v>261</v>
       </c>
       <c r="D246" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5329,7 +5320,7 @@
         <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5343,7 +5334,7 @@
         <v>261</v>
       </c>
       <c r="D248" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5357,7 +5348,7 @@
         <v>261</v>
       </c>
       <c r="D249" t="s">
-        <v>494</v>
+        <v>491</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5371,7 +5362,7 @@
         <v>261</v>
       </c>
       <c r="D250" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5385,7 +5376,7 @@
         <v>259</v>
       </c>
       <c r="D251" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5399,7 +5390,7 @@
         <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5413,7 +5404,7 @@
         <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>498</v>
+        <v>495</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5427,7 +5418,7 @@
         <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>396</v>
+        <v>339</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5441,7 +5432,7 @@
         <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>396</v>
+        <v>339</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5455,7 +5446,7 @@
         <v>259</v>
       </c>
       <c r="D256" t="s">
-        <v>499</v>
+        <v>496</v>
       </c>
     </row>
   </sheetData>

--- a/dataset_agreed/saved_models/baserun/pointcloud_base_run10/epoch_80/per_file_predictions_epoch_80.xlsx
+++ b/dataset_agreed/saved_models/baserun/pointcloud_base_run10/epoch_80/per_file_predictions_epoch_80.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="497">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="492">
   <si>
     <t>Filename</t>
   </si>
@@ -808,703 +808,688 @@
     <t>0,1,1,0</t>
   </si>
   <si>
+    <t>1,0,1,0</t>
+  </si>
+  <si>
     <t>0,1,0,1</t>
   </si>
   <si>
-    <t>0.9863,0.0041,0.0017,0.0005</t>
-  </si>
-  <si>
-    <t>0.0001,0.0003,0.0000,0.9999</t>
-  </si>
-  <si>
-    <t>0.9887,0.0001,0.0000,0.0109</t>
-  </si>
-  <si>
-    <t>0.0310,0.0000,0.0011,0.9856</t>
-  </si>
-  <si>
-    <t>0.9996,0.0002,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9992,0.0005,0.0000,0.0000</t>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
+    <t>0.9636,0.0061,0.0072,0.0016</t>
+  </si>
+  <si>
+    <t>0.0001,0.0001,0.0000,0.9999</t>
+  </si>
+  <si>
+    <t>0.9906,0.0005,0.0005,0.0040</t>
+  </si>
+  <si>
+    <t>0.0099,0.0000,0.0003,0.9965</t>
+  </si>
+  <si>
+    <t>0.9996,0.0001,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9993,0.0004,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9981,0.0007,0.0002,0.0002</t>
+  </si>
+  <si>
+    <t>0.9999,0.0000,0.0000,0.0000</t>
   </si>
   <si>
     <t>0.9997,0.0001,0.0000,0.0000</t>
   </si>
   <si>
+    <t>0.9985,0.0008,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>1.0000,0.0000,0.0000,0.0000</t>
+  </si>
+  <si>
     <t>0.9998,0.0001,0.0000,0.0000</t>
   </si>
   <si>
-    <t>0.9994,0.0003,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>1.0000,0.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9623,0.0007,0.0323,0.0003</t>
-  </si>
-  <si>
-    <t>0.1269,0.0007,0.9420,0.0000</t>
-  </si>
-  <si>
-    <t>0.0593,0.0003,0.9708,0.0000</t>
-  </si>
-  <si>
-    <t>0.0129,0.0012,0.9880,0.0002</t>
-  </si>
-  <si>
-    <t>0.9877,0.0004,0.0038,0.0007</t>
+    <t>0.8896,0.0159,0.0420,0.0010</t>
+  </si>
+  <si>
+    <t>0.5213,0.0008,0.5146,0.0006</t>
+  </si>
+  <si>
+    <t>0.5385,0.0018,0.6044,0.0001</t>
+  </si>
+  <si>
+    <t>0.0006,0.0001,0.9991,0.0001</t>
+  </si>
+  <si>
+    <t>0.9878,0.0001,0.0091,0.0002</t>
+  </si>
+  <si>
+    <t>0.0001,0.9998,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0007,0.9986,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.0092,0.9889,0.0006,0.0002</t>
+  </si>
+  <si>
+    <t>0.0002,0.9994,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.3913,0.0027,0.5552,0.0017</t>
+  </si>
+  <si>
+    <t>0.1395,0.0004,0.9048,0.0002</t>
+  </si>
+  <si>
+    <t>0.0003,0.0000,0.9996,0.0001</t>
+  </si>
+  <si>
+    <t>0.0034,0.0013,0.9909,0.0004</t>
+  </si>
+  <si>
+    <t>0.0014,0.0000,0.9988,0.0001</t>
+  </si>
+  <si>
+    <t>0.0002,0.0000,0.9996,0.0001</t>
+  </si>
+  <si>
+    <t>0.0004,0.0000,0.9997,0.0000</t>
+  </si>
+  <si>
+    <t>0.8321,0.1750,0.0007,0.0001</t>
+  </si>
+  <si>
+    <t>0.9462,0.0420,0.0074,0.0005</t>
+  </si>
+  <si>
+    <t>0.0007,0.0012,0.9991,0.0013</t>
+  </si>
+  <si>
+    <t>0.0012,0.9967,0.0029,0.0000</t>
+  </si>
+  <si>
+    <t>0.9918,0.0035,0.0004,0.0003</t>
+  </si>
+  <si>
+    <t>0.9780,0.0012,0.0157,0.0003</t>
+  </si>
+  <si>
+    <t>0.2161,0.8372,0.0008,0.0001</t>
+  </si>
+  <si>
+    <t>0.0004,0.9972,0.0240,0.0000</t>
+  </si>
+  <si>
+    <t>0.0105,0.5746,0.2537,0.0012</t>
+  </si>
+  <si>
+    <t>0.0005,0.0007,0.9978,0.0003</t>
+  </si>
+  <si>
+    <t>0.0012,0.0075,0.9952,0.0001</t>
+  </si>
+  <si>
+    <t>0.0012,0.0000,0.9971,0.0003</t>
+  </si>
+  <si>
+    <t>0.0013,0.0131,0.9975,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0004,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.0001,0.9990,0.0012</t>
+  </si>
+  <si>
+    <t>0.0383,0.2688,0.0001,0.6290</t>
+  </si>
+  <si>
+    <t>0.0011,0.9973,0.0001,0.0003</t>
+  </si>
+  <si>
+    <t>0.0036,0.9924,0.0029,0.0001</t>
+  </si>
+  <si>
+    <t>0.0003,0.9992,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,1.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0005,0.0037,0.9981,0.0001</t>
+  </si>
+  <si>
+    <t>0.0006,0.0012,0.9966,0.0033</t>
+  </si>
+  <si>
+    <t>0.0048,0.0000,0.9967,0.0000</t>
+  </si>
+  <si>
+    <t>0.0006,0.0003,0.9992,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,0.9999,0.0002</t>
+  </si>
+  <si>
+    <t>0.9972,0.0020,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9983,0.0002,0.0005,0.0001</t>
+  </si>
+  <si>
+    <t>0.9908,0.0038,0.0036,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.0028,0.9998,0.0002</t>
+  </si>
+  <si>
+    <t>0.9989,0.0005,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9926,0.0066,0.0004,0.0002</t>
+  </si>
+  <si>
+    <t>0.9998,0.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9801,0.9951,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0006,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0004,0.0001,0.9990,0.0002</t>
+  </si>
+  <si>
+    <t>0.0000,0.9980,0.9982,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0002,0.9998,0.0001</t>
+  </si>
+  <si>
+    <t>0.0008,0.9987,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9980,0.0001,0.0011,0.0000</t>
+  </si>
+  <si>
+    <t>0.0073,0.0004,0.9928,0.0002</t>
+  </si>
+  <si>
+    <t>0.0004,0.0021,0.9992,0.0008</t>
+  </si>
+  <si>
+    <t>0.0000,0.9930,0.9797,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.9257,0.9289,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.9615,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9979,0.9965,0.0000</t>
+  </si>
+  <si>
+    <t>0.0014,0.0001,0.0011,0.9988</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.0000,0.0000,0.9999</t>
+  </si>
+  <si>
+    <t>0.0001,0.0000,0.0018,0.9994</t>
+  </si>
+  <si>
+    <t>0.0002,0.0001,0.0006,0.9997</t>
+  </si>
+  <si>
+    <t>0.0000,0.9973,0.9967,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9940,0.9843,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9953,0.7404,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9988,0.9986,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9936,0.9979,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9920,0.6936,0.0000</t>
+  </si>
+  <si>
+    <t>0.9987,0.0012,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9964,0.0024,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9958,0.0029,0.0004,0.0001</t>
+  </si>
+  <si>
+    <t>0.9928,0.0047,0.0006,0.0003</t>
+  </si>
+  <si>
+    <t>0.9995,0.0005,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9974,0.0023,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9963,0.0015,0.0002,0.0005</t>
+  </si>
+  <si>
+    <t>0.0053,0.0006,0.9961,0.0001</t>
+  </si>
+  <si>
+    <t>0.0005,0.0006,0.9988,0.0001</t>
+  </si>
+  <si>
+    <t>0.8966,0.0018,0.0645,0.0023</t>
+  </si>
+  <si>
+    <t>0.1428,0.0001,0.8857,0.0004</t>
   </si>
   <si>
     <t>0.0001,0.9997,0.0001,0.0000</t>
   </si>
   <si>
-    <t>0.0003,0.9992,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.0024,0.9954,0.0010,0.0001</t>
-  </si>
-  <si>
-    <t>0.0003,0.9991,0.0002,0.0006</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9061,0.0006,0.0893,0.0007</t>
-  </si>
-  <si>
-    <t>0.0510,0.0006,0.9500,0.0006</t>
-  </si>
-  <si>
-    <t>0.0016,0.0001,0.9980,0.0001</t>
-  </si>
-  <si>
-    <t>0.0123,0.0007,0.9868,0.0002</t>
-  </si>
-  <si>
-    <t>0.3461,0.0001,0.7629,0.0002</t>
-  </si>
-  <si>
-    <t>0.0003,0.0000,0.9995,0.0000</t>
-  </si>
-  <si>
-    <t>0.1195,0.0000,0.9381,0.0001</t>
-  </si>
-  <si>
-    <t>0.1790,0.8426,0.0008,0.0001</t>
-  </si>
-  <si>
-    <t>0.7052,0.2814,0.0189,0.0005</t>
-  </si>
-  <si>
-    <t>0.0029,0.0021,0.9977,0.0020</t>
-  </si>
-  <si>
-    <t>0.0005,0.9990,0.0005,0.0000</t>
-  </si>
-  <si>
-    <t>0.9952,0.0007,0.0009,0.0005</t>
-  </si>
-  <si>
-    <t>0.9873,0.0008,0.0076,0.0003</t>
-  </si>
-  <si>
-    <t>0.0056,0.9923,0.0005,0.0001</t>
-  </si>
-  <si>
-    <t>0.0002,0.9964,0.1249,0.0000</t>
-  </si>
-  <si>
-    <t>0.0003,0.9987,0.0008,0.0001</t>
-  </si>
-  <si>
-    <t>0.0132,0.0037,0.9706,0.0017</t>
-  </si>
-  <si>
-    <t>0.0031,0.0108,0.9898,0.0003</t>
-  </si>
-  <si>
-    <t>0.0005,0.0000,0.9944,0.0013</t>
-  </si>
-  <si>
-    <t>0.0002,0.0105,0.9991,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9998,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0002,0.9993,0.0076</t>
-  </si>
-  <si>
-    <t>0.0005,0.8870,0.0005,0.9751</t>
-  </si>
-  <si>
-    <t>0.0005,0.9963,0.0000,0.0020</t>
-  </si>
-  <si>
-    <t>0.0005,0.9988,0.0007,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9998,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0003,0.9999,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.0023,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0003,0.0001,0.9989,0.0003</t>
-  </si>
-  <si>
-    <t>0.0045,0.0000,0.9973,0.0000</t>
-  </si>
-  <si>
-    <t>0.0005,0.0002,0.9994,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,0.9999,0.0001</t>
-  </si>
-  <si>
-    <t>0.9980,0.0014,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9994,0.0001,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9778,0.0026,0.0165,0.0002</t>
-  </si>
-  <si>
-    <t>0.0001,0.0006,0.9999,0.0002</t>
-  </si>
-  <si>
-    <t>0.9975,0.0018,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.9753,0.0327,0.0005,0.0001</t>
-  </si>
-  <si>
-    <t>0.9987,0.0004,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9685,0.9972,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0031,0.9998,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.0003,0.9991,0.0004</t>
-  </si>
-  <si>
-    <t>0.0000,0.9984,0.9996,0.0000</t>
-  </si>
-  <si>
-    <t>0.0005,0.0001,0.9989,0.0010</t>
-  </si>
-  <si>
-    <t>0.0050,0.9923,0.0014,0.0000</t>
-  </si>
-  <si>
-    <t>0.9772,0.0001,0.0291,0.0001</t>
-  </si>
-  <si>
-    <t>0.1264,0.0003,0.9293,0.0001</t>
-  </si>
-  <si>
-    <t>0.0003,0.0049,0.9995,0.0006</t>
-  </si>
-  <si>
-    <t>0.0000,0.9977,0.9978,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9522,0.9812,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9998,0.2999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9987,0.9910,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0000,0.0027,0.9996</t>
-  </si>
-  <si>
-    <t>0.0000,0.0003,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,0.0048,0.9998</t>
-  </si>
-  <si>
-    <t>0.0004,0.0000,0.0004,0.9996</t>
-  </si>
-  <si>
-    <t>0.0004,0.0001,0.0000,0.9997</t>
-  </si>
-  <si>
-    <t>0.0000,0.9969,0.9968,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9969,0.9982,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9922,0.9929,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9863,0.9980,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9868,0.9990,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.8360,0.9696,0.0000</t>
-  </si>
-  <si>
-    <t>0.9994,0.0004,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9992,0.0001,0.0000,0.0002</t>
-  </si>
-  <si>
-    <t>0.9974,0.0011,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9930,0.0072,0.0006,0.0001</t>
-  </si>
-  <si>
-    <t>0.9959,0.0021,0.0004,0.0003</t>
-  </si>
-  <si>
-    <t>0.9976,0.0022,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.9999,0.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9998,0.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9972,0.0021,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9976,0.0013,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.0005,0.0004,0.9993,0.0004</t>
-  </si>
-  <si>
-    <t>0.0089,0.0003,0.9918,0.0002</t>
-  </si>
-  <si>
-    <t>0.9919,0.0002,0.0015,0.0003</t>
-  </si>
-  <si>
-    <t>0.2143,0.0004,0.8649,0.0002</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0013,0.9972,0.0006,0.0001</t>
-  </si>
-  <si>
-    <t>0.0005,0.9987,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.1289,0.8798,0.0035,0.0002</t>
-  </si>
-  <si>
-    <t>0.5956,0.0050,0.3396,0.0017</t>
-  </si>
-  <si>
-    <t>0.7713,0.0004,0.2751,0.0003</t>
-  </si>
-  <si>
-    <t>0.9355,0.0046,0.0142,0.0034</t>
-  </si>
-  <si>
-    <t>0.9875,0.0013,0.0020,0.0003</t>
-  </si>
-  <si>
-    <t>0.0011,0.8752,0.0147,0.6918</t>
-  </si>
-  <si>
-    <t>0.0001,0.9996,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9997,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9969,0.8480,0.0000</t>
-  </si>
-  <si>
-    <t>0.1538,0.8673,0.0010,0.0002</t>
-  </si>
-  <si>
-    <t>0.8950,0.1283,0.0030,0.0001</t>
-  </si>
-  <si>
-    <t>0.9971,0.0011,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9985,0.0001,0.0000,0.0007</t>
+    <t>0.0002,0.9992,0.0005,0.0000</t>
+  </si>
+  <si>
+    <t>0.0017,0.9965,0.0009,0.0002</t>
+  </si>
+  <si>
+    <t>0.0477,0.9576,0.0010,0.0001</t>
+  </si>
+  <si>
+    <t>0.0873,0.0018,0.8971,0.0023</t>
+  </si>
+  <si>
+    <t>0.8758,0.0003,0.1142,0.0006</t>
+  </si>
+  <si>
+    <t>0.9806,0.0020,0.0035,0.0001</t>
+  </si>
+  <si>
+    <t>0.9427,0.0038,0.0255,0.0011</t>
+  </si>
+  <si>
+    <t>0.0003,0.9748,0.0015,0.6135</t>
+  </si>
+  <si>
+    <t>0.0002,0.9993,0.0005,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9998,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9961,0.9805,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9999,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0157,0.9834,0.0008,0.0000</t>
+  </si>
+  <si>
+    <t>0.6657,0.3644,0.0063,0.0004</t>
+  </si>
+  <si>
+    <t>0.9991,0.0003,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9991,0.0002,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9991,0.0000,0.0000,0.0011</t>
+  </si>
+  <si>
+    <t>0.9996,0.0000,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9997,0.0000,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9995,0.0001,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9976,0.0002,0.0001,0.0010</t>
   </si>
   <si>
     <t>0.9995,0.0000,0.0001,0.0001</t>
   </si>
   <si>
-    <t>0.9990,0.0001,0.0001,0.0003</t>
-  </si>
-  <si>
-    <t>0.9960,0.0007,0.0011,0.0001</t>
-  </si>
-  <si>
-    <t>0.9957,0.0010,0.0004,0.0008</t>
-  </si>
-  <si>
-    <t>0.9995,0.0001,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9347,0.9980,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.4249,0.9994,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0034,0.9994,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0001,0.9997,0.0001</t>
-  </si>
-  <si>
-    <t>0.9986,0.0000,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.8078,0.0038,0.1399,0.0034</t>
-  </si>
-  <si>
-    <t>0.3290,0.0000,0.8747,0.0000</t>
-  </si>
-  <si>
-    <t>0.9118,0.0006,0.0886,0.0008</t>
-  </si>
-  <si>
-    <t>0.0088,0.0001,0.0000,0.9984</t>
-  </si>
-  <si>
-    <t>0.0000,0.0001,0.0001,1.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9959,0.1316,0.0000</t>
-  </si>
-  <si>
-    <t>0.9981,0.0005,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.0013,0.9965,0.0005,0.0016</t>
-  </si>
-  <si>
-    <t>0.9996,0.0000,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.0779,0.9447,0.0009,0.0000</t>
-  </si>
-  <si>
-    <t>0.9995,0.0000,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.9193,0.0002,0.0044,0.0315</t>
+    <t>0.0000,0.9866,0.9974,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.3570,0.9972,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.0050,0.9987,0.0000</t>
+  </si>
+  <si>
+    <t>0.0005,0.0040,0.9984,0.0000</t>
+  </si>
+  <si>
+    <t>0.9995,0.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9736,0.0018,0.0048,0.0015</t>
+  </si>
+  <si>
+    <t>0.0066,0.0002,0.9952,0.0001</t>
+  </si>
+  <si>
+    <t>0.8824,0.0015,0.1042,0.0015</t>
+  </si>
+  <si>
+    <t>0.0417,0.0000,0.0000,0.9950</t>
+  </si>
+  <si>
+    <t>0.0000,0.0001,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.9366,0.8586,0.0000</t>
+  </si>
+  <si>
+    <t>0.0018,0.9972,0.0002,0.0002</t>
+  </si>
+  <si>
+    <t>0.3124,0.8067,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.9977,0.0001,0.0010,0.0001</t>
+  </si>
+  <si>
+    <t>0.7272,0.0001,0.0001,0.3353</t>
+  </si>
+  <si>
+    <t>0.0010,0.0012,0.9950,0.0143</t>
   </si>
   <si>
     <t>0.9996,0.0000,0.0001,0.0000</t>
   </si>
   <si>
-    <t>0.0011,0.0012,0.9967,0.0038</t>
-  </si>
-  <si>
-    <t>0.9979,0.0000,0.0008,0.0001</t>
-  </si>
-  <si>
-    <t>0.9943,0.0001,0.0038,0.0002</t>
-  </si>
-  <si>
-    <t>0.0690,0.9213,0.0046,0.0005</t>
-  </si>
-  <si>
-    <t>0.9979,0.0002,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9664,0.0066,0.0100,0.0010</t>
-  </si>
-  <si>
-    <t>0.1517,0.0297,0.6006,0.0013</t>
-  </si>
-  <si>
-    <t>0.5980,0.0062,0.3972,0.0003</t>
-  </si>
-  <si>
-    <t>0.9826,0.0023,0.0045,0.0003</t>
-  </si>
-  <si>
-    <t>0.9967,0.0003,0.0013,0.0002</t>
-  </si>
-  <si>
-    <t>0.9995,0.0001,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9987,0.0003,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9992,0.0001,0.0002,0.0002</t>
-  </si>
-  <si>
-    <t>0.9993,0.0001,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9911,0.0039,0.0008,0.0009</t>
-  </si>
-  <si>
-    <t>0.9996,0.0001,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9986,0.0000,0.0003,0.0003</t>
-  </si>
-  <si>
-    <t>0.9621,0.0223,0.0002,0.0007</t>
-  </si>
-  <si>
-    <t>0.7959,0.2963,0.0004,0.0000</t>
-  </si>
-  <si>
-    <t>0.9836,0.0137,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.1074,0.0004,0.9136,0.0015</t>
-  </si>
-  <si>
-    <t>0.9933,0.0062,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.9959,0.0007,0.0006,0.0011</t>
-  </si>
-  <si>
-    <t>0.9956,0.0019,0.0010,0.0001</t>
-  </si>
-  <si>
-    <t>0.9645,0.0046,0.0187,0.0008</t>
-  </si>
-  <si>
-    <t>0.0003,0.0001,0.9998,0.0000</t>
-  </si>
-  <si>
-    <t>0.9344,0.0218,0.0266,0.0004</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,1.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0016,0.0031,0.9935,0.0019</t>
-  </si>
-  <si>
-    <t>0.0001,0.0003,0.9998,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.0219,0.9986,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.0004,0.9998,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0003,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0053,0.0008,0.9907,0.0002</t>
-  </si>
-  <si>
-    <t>0.8475,0.0043,0.1320,0.0008</t>
-  </si>
-  <si>
-    <t>0.0220,0.0069,0.9640,0.0004</t>
-  </si>
-  <si>
-    <t>0.0509,0.0050,0.9348,0.0003</t>
-  </si>
-  <si>
-    <t>0.0371,0.0165,0.9209,0.0002</t>
-  </si>
-  <si>
-    <t>0.6372,0.0039,0.4643,0.0003</t>
-  </si>
-  <si>
-    <t>0.8968,0.0054,0.0369,0.0052</t>
-  </si>
-  <si>
-    <t>0.2868,0.0013,0.7660,0.0005</t>
-  </si>
-  <si>
-    <t>0.0080,0.9901,0.0009,0.0000</t>
-  </si>
-  <si>
-    <t>0.7146,0.3907,0.0006,0.0000</t>
-  </si>
-  <si>
-    <t>0.0921,0.9234,0.0011,0.0001</t>
-  </si>
-  <si>
-    <t>0.0053,0.9934,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.9834,0.0007,0.0055,0.0002</t>
-  </si>
-  <si>
-    <t>0.8747,0.0001,0.1332,0.0008</t>
-  </si>
-  <si>
-    <t>0.9861,0.0005,0.0008,0.0013</t>
-  </si>
-  <si>
-    <t>0.6137,0.0103,0.3049,0.0091</t>
-  </si>
-  <si>
-    <t>0.0351,0.0015,0.9552,0.0019</t>
-  </si>
-  <si>
-    <t>0.0017,0.0006,0.9978,0.0002</t>
-  </si>
-  <si>
-    <t>0.0009,0.0009,0.9962,0.0003</t>
-  </si>
-  <si>
-    <t>0.0062,0.0046,0.9817,0.0010</t>
-  </si>
-  <si>
-    <t>0.0020,0.0013,0.9952,0.0001</t>
-  </si>
-  <si>
-    <t>0.0002,0.0027,0.9977,0.0005</t>
-  </si>
-  <si>
-    <t>0.9985,0.0001,0.0000,0.0004</t>
-  </si>
-  <si>
-    <t>0.9850,0.0167,0.0011,0.0003</t>
-  </si>
-  <si>
-    <t>0.9883,0.0033,0.0017,0.0037</t>
-  </si>
-  <si>
-    <t>0.9989,0.0007,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9974,0.0014,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9993,0.0004,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9982,0.0006,0.0002,0.0003</t>
-  </si>
-  <si>
-    <t>0.9988,0.0004,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.0006,0.0004,0.9987,0.0008</t>
-  </si>
-  <si>
-    <t>0.0037,0.0243,0.9728,0.0015</t>
-  </si>
-  <si>
-    <t>0.8841,0.0005,0.0501,0.0056</t>
-  </si>
-  <si>
-    <t>0.0035,0.0016,0.9967,0.0001</t>
-  </si>
-  <si>
-    <t>0.0002,0.0003,0.9998,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.8774,0.9819,0.0001</t>
-  </si>
-  <si>
-    <t>0.0004,0.0001,0.9992,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.0001,1.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0004,0.0006,0.9988,0.0003</t>
-  </si>
-  <si>
-    <t>0.0005,0.0035,0.9972,0.0005</t>
-  </si>
-  <si>
-    <t>0.9743,0.0027,0.0072,0.0003</t>
-  </si>
-  <si>
-    <t>0.9280,0.0008,0.0582,0.0010</t>
-  </si>
-  <si>
-    <t>0.9921,0.0002,0.0023,0.0001</t>
-  </si>
-  <si>
-    <t>0.9972,0.0014,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9934,0.0055,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.9969,0.0029,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9986,0.0011,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9971,0.0015,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9985,0.0004,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.0022,0.0036,0.9939,0.0002</t>
-  </si>
-  <si>
-    <t>0.0036,0.0059,0.9895,0.0006</t>
-  </si>
-  <si>
-    <t>0.0000,0.9979,0.9527,0.0000</t>
-  </si>
-  <si>
-    <t>0.0057,0.0017,0.9876,0.0012</t>
-  </si>
-  <si>
-    <t>0.0024,0.0001,0.9983,0.0001</t>
-  </si>
-  <si>
-    <t>0.0047,0.0002,0.9868,0.0024</t>
-  </si>
-  <si>
-    <t>0.0136,0.0008,0.9839,0.0004</t>
-  </si>
-  <si>
-    <t>0.0060,0.0008,0.9835,0.0044</t>
-  </si>
-  <si>
-    <t>0.9034,0.0001,0.0149,0.0257</t>
-  </si>
-  <si>
-    <t>0.0004,0.0011,0.0000,0.9998</t>
-  </si>
-  <si>
-    <t>0.0341,0.0000,0.0000,0.9974</t>
-  </si>
-  <si>
-    <t>0.9979,0.0001,0.0001,0.0002</t>
+    <t>0.9992,0.0000,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.2330,0.7378,0.0093,0.0001</t>
+  </si>
+  <si>
+    <t>0.9965,0.0003,0.0004,0.0004</t>
+  </si>
+  <si>
+    <t>0.9831,0.0025,0.0054,0.0004</t>
+  </si>
+  <si>
+    <t>0.0224,0.9511,0.0118,0.0011</t>
+  </si>
+  <si>
+    <t>0.9405,0.0060,0.0297,0.0004</t>
+  </si>
+  <si>
+    <t>0.9838,0.0030,0.0022,0.0003</t>
+  </si>
+  <si>
+    <t>0.9982,0.0004,0.0003,0.0002</t>
+  </si>
+  <si>
+    <t>0.9933,0.0011,0.0006,0.0023</t>
+  </si>
+  <si>
+    <t>0.9993,0.0001,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9993,0.0001,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9892,0.0063,0.0003,0.0005</t>
+  </si>
+  <si>
+    <t>0.8426,0.2395,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.9827,0.0116,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9681,0.0033,0.0161,0.0004</t>
+  </si>
+  <si>
+    <t>0.9984,0.0006,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9984,0.0002,0.0001,0.0004</t>
+  </si>
+  <si>
+    <t>0.9947,0.0032,0.0010,0.0001</t>
+  </si>
+  <si>
+    <t>0.9725,0.0203,0.0060,0.0004</t>
+  </si>
+  <si>
+    <t>0.0013,0.0004,0.9994,0.0001</t>
+  </si>
+  <si>
+    <t>0.9919,0.0055,0.0014,0.0001</t>
+  </si>
+  <si>
+    <t>0.0333,0.0386,0.8740,0.0010</t>
+  </si>
+  <si>
+    <t>0.0002,0.0002,0.9997,0.0000</t>
+  </si>
+  <si>
+    <t>0.0004,0.1608,0.9937,0.0001</t>
+  </si>
+  <si>
+    <t>0.0003,0.0003,0.9996,0.0001</t>
+  </si>
+  <si>
+    <t>0.0338,0.0018,0.9586,0.0006</t>
+  </si>
+  <si>
+    <t>0.0962,0.0011,0.9271,0.0003</t>
+  </si>
+  <si>
+    <t>0.7692,0.0372,0.0918,0.0014</t>
+  </si>
+  <si>
+    <t>0.0237,0.0053,0.9601,0.0003</t>
+  </si>
+  <si>
+    <t>0.0176,0.0228,0.9377,0.0003</t>
+  </si>
+  <si>
+    <t>0.7793,0.0075,0.2418,0.0004</t>
+  </si>
+  <si>
+    <t>0.9712,0.0012,0.0112,0.0008</t>
+  </si>
+  <si>
+    <t>0.0866,0.0009,0.9160,0.0007</t>
+  </si>
+  <si>
+    <t>0.0044,0.9945,0.0004,0.0000</t>
+  </si>
+  <si>
+    <t>0.0016,0.9981,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.6045,0.4752,0.0011,0.0001</t>
+  </si>
+  <si>
+    <t>0.0579,0.9538,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.0590,0.9455,0.0007,0.0001</t>
+  </si>
+  <si>
+    <t>0.8223,0.0367,0.0577,0.0005</t>
+  </si>
+  <si>
+    <t>0.4505,0.0001,0.5755,0.0005</t>
+  </si>
+  <si>
+    <t>0.9400,0.0002,0.0083,0.0115</t>
+  </si>
+  <si>
+    <t>0.4609,0.0122,0.4922,0.0043</t>
+  </si>
+  <si>
+    <t>0.7934,0.0011,0.2108,0.0008</t>
+  </si>
+  <si>
+    <t>0.0012,0.0007,0.9983,0.0003</t>
+  </si>
+  <si>
+    <t>0.0003,0.0002,0.9978,0.0017</t>
+  </si>
+  <si>
+    <t>0.0062,0.0118,0.9768,0.0013</t>
+  </si>
+  <si>
+    <t>0.0006,0.0002,0.9989,0.0001</t>
+  </si>
+  <si>
+    <t>0.0006,0.0226,0.9882,0.0005</t>
+  </si>
+  <si>
+    <t>0.9975,0.0010,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9617,0.0357,0.0042,0.0014</t>
+  </si>
+  <si>
+    <t>0.9992,0.0004,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9984,0.0007,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9946,0.0039,0.0004,0.0001</t>
+  </si>
+  <si>
+    <t>0.9975,0.0016,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9997,0.0001,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.0003,0.0019,0.9989,0.0005</t>
+  </si>
+  <si>
+    <t>0.0344,0.0326,0.9153,0.0011</t>
+  </si>
+  <si>
+    <t>0.9790,0.0005,0.0070,0.0025</t>
+  </si>
+  <si>
+    <t>0.0016,0.0004,0.9988,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0012,0.9998,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.8366,0.9964,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.0000,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0035,0.0004,0.9948,0.0001</t>
+  </si>
+  <si>
+    <t>0.0016,0.0015,0.9955,0.0006</t>
+  </si>
+  <si>
+    <t>0.0030,0.0228,0.9852,0.0007</t>
+  </si>
+  <si>
+    <t>0.9832,0.0004,0.0056,0.0007</t>
+  </si>
+  <si>
+    <t>0.9915,0.0002,0.0027,0.0001</t>
+  </si>
+  <si>
+    <t>0.9891,0.0003,0.0036,0.0002</t>
+  </si>
+  <si>
+    <t>0.9977,0.0013,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9991,0.0006,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9938,0.0066,0.0005,0.0000</t>
+  </si>
+  <si>
+    <t>0.9995,0.0003,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9966,0.0020,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.9994,0.0001,0.0000,0.0002</t>
+  </si>
+  <si>
+    <t>0.0181,0.0525,0.8182,0.0029</t>
+  </si>
+  <si>
+    <t>0.0005,0.0002,0.9989,0.0001</t>
+  </si>
+  <si>
+    <t>0.0004,0.0690,0.9933,0.0002</t>
+  </si>
+  <si>
+    <t>0.0008,0.1366,0.9530,0.0002</t>
+  </si>
+  <si>
+    <t>0.0011,0.0003,0.9982,0.0002</t>
+  </si>
+  <si>
+    <t>0.0007,0.0004,0.9970,0.0024</t>
+  </si>
+  <si>
+    <t>0.4828,0.0005,0.5361,0.0009</t>
+  </si>
+  <si>
+    <t>0.0003,0.0001,0.9988,0.0014</t>
+  </si>
+  <si>
+    <t>0.9656,0.0000,0.0006,0.0331</t>
+  </si>
+  <si>
+    <t>0.0011,0.0004,0.0000,0.9997</t>
+  </si>
+  <si>
+    <t>0.0063,0.0000,0.0000,0.9991</t>
+  </si>
+  <si>
+    <t>0.0001,0.0000,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.9926,0.0002,0.0003,0.0012</t>
   </si>
 </sst>
 </file>
@@ -1890,7 +1875,7 @@
         <v>259</v>
       </c>
       <c r="D2" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1904,7 +1889,7 @@
         <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1918,7 +1903,7 @@
         <v>259</v>
       </c>
       <c r="D4" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1932,7 +1917,7 @@
         <v>260</v>
       </c>
       <c r="D5" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -1946,7 +1931,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -1960,7 +1945,7 @@
         <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -1974,7 +1959,7 @@
         <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -1988,7 +1973,7 @@
         <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2002,7 +1987,7 @@
         <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2016,7 +2001,7 @@
         <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2030,7 +2015,7 @@
         <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2044,7 +2029,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2058,7 +2043,7 @@
         <v>259</v>
       </c>
       <c r="D14" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2069,10 +2054,10 @@
         <v>261</v>
       </c>
       <c r="C15" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D15" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2083,10 +2068,10 @@
         <v>261</v>
       </c>
       <c r="C16" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D16" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2100,7 +2085,7 @@
         <v>261</v>
       </c>
       <c r="D17" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2114,7 +2099,7 @@
         <v>259</v>
       </c>
       <c r="D18" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2128,7 +2113,7 @@
         <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2142,7 +2127,7 @@
         <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2156,7 +2141,7 @@
         <v>262</v>
       </c>
       <c r="D21" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2170,7 +2155,7 @@
         <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2184,7 +2169,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2195,10 +2180,10 @@
         <v>259</v>
       </c>
       <c r="C24" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D24" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2212,7 +2197,7 @@
         <v>261</v>
       </c>
       <c r="D25" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2226,7 +2211,7 @@
         <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2240,7 +2225,7 @@
         <v>261</v>
       </c>
       <c r="D27" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2254,7 +2239,7 @@
         <v>261</v>
       </c>
       <c r="D28" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2268,7 +2253,7 @@
         <v>261</v>
       </c>
       <c r="D29" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2282,7 +2267,7 @@
         <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2293,10 +2278,10 @@
         <v>259</v>
       </c>
       <c r="C31" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D31" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2310,7 +2295,7 @@
         <v>259</v>
       </c>
       <c r="D32" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2324,7 +2309,7 @@
         <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2338,7 +2323,7 @@
         <v>262</v>
       </c>
       <c r="D34" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2352,7 +2337,7 @@
         <v>259</v>
       </c>
       <c r="D35" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2366,7 +2351,7 @@
         <v>259</v>
       </c>
       <c r="D36" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2380,7 +2365,7 @@
         <v>262</v>
       </c>
       <c r="D37" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2394,7 +2379,7 @@
         <v>262</v>
       </c>
       <c r="D38" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2408,7 +2393,7 @@
         <v>262</v>
       </c>
       <c r="D39" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2422,7 +2407,7 @@
         <v>261</v>
       </c>
       <c r="D40" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2436,7 +2421,7 @@
         <v>261</v>
       </c>
       <c r="D41" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2450,7 +2435,7 @@
         <v>261</v>
       </c>
       <c r="D42" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2464,7 +2449,7 @@
         <v>261</v>
       </c>
       <c r="D43" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2478,7 +2463,7 @@
         <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2492,7 +2477,7 @@
         <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2503,10 +2488,10 @@
         <v>259</v>
       </c>
       <c r="C46" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="D46" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2520,7 +2505,7 @@
         <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2534,7 +2519,7 @@
         <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2548,7 +2533,7 @@
         <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2562,7 +2547,7 @@
         <v>261</v>
       </c>
       <c r="D50" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2576,7 +2561,7 @@
         <v>261</v>
       </c>
       <c r="D51" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2590,7 +2575,7 @@
         <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2604,7 +2589,7 @@
         <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2618,7 +2603,7 @@
         <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2632,7 +2617,7 @@
         <v>261</v>
       </c>
       <c r="D55" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2646,7 +2631,7 @@
         <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2660,7 +2645,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2674,7 +2659,7 @@
         <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2688,7 +2673,7 @@
         <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2702,7 +2687,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2716,7 +2701,7 @@
         <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2730,7 +2715,7 @@
         <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2744,7 +2729,7 @@
         <v>263</v>
       </c>
       <c r="D63" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2758,7 +2743,7 @@
         <v>261</v>
       </c>
       <c r="D64" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2772,7 +2757,7 @@
         <v>261</v>
       </c>
       <c r="D65" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2786,7 +2771,7 @@
         <v>263</v>
       </c>
       <c r="D66" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2800,7 +2785,7 @@
         <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2814,7 +2799,7 @@
         <v>262</v>
       </c>
       <c r="D68" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2828,7 +2813,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>310</v>
+        <v>334</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2842,7 +2827,7 @@
         <v>259</v>
       </c>
       <c r="D70" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2856,7 +2841,7 @@
         <v>261</v>
       </c>
       <c r="D71" t="s">
-        <v>331</v>
+        <v>336</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2870,7 +2855,7 @@
         <v>261</v>
       </c>
       <c r="D72" t="s">
-        <v>332</v>
+        <v>337</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2884,7 +2869,7 @@
         <v>263</v>
       </c>
       <c r="D73" t="s">
-        <v>333</v>
+        <v>338</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2898,7 +2883,7 @@
         <v>263</v>
       </c>
       <c r="D74" t="s">
-        <v>334</v>
+        <v>339</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2909,10 +2894,10 @@
         <v>262</v>
       </c>
       <c r="C75" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D75" t="s">
-        <v>335</v>
+        <v>340</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2926,7 +2911,7 @@
         <v>263</v>
       </c>
       <c r="D76" t="s">
-        <v>336</v>
+        <v>341</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -2940,7 +2925,7 @@
         <v>260</v>
       </c>
       <c r="D77" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -2954,7 +2939,7 @@
         <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -2968,7 +2953,7 @@
         <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -2982,7 +2967,7 @@
         <v>260</v>
       </c>
       <c r="D80" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -2996,7 +2981,7 @@
         <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>341</v>
+        <v>346</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -3010,7 +2995,7 @@
         <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3024,7 +3009,7 @@
         <v>263</v>
       </c>
       <c r="D83" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3038,7 +3023,7 @@
         <v>263</v>
       </c>
       <c r="D84" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3052,7 +3037,7 @@
         <v>263</v>
       </c>
       <c r="D85" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3066,7 +3051,7 @@
         <v>263</v>
       </c>
       <c r="D86" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3080,7 +3065,7 @@
         <v>263</v>
       </c>
       <c r="D87" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3094,7 +3079,7 @@
         <v>263</v>
       </c>
       <c r="D88" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3108,7 +3093,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3122,7 +3107,7 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3136,7 +3121,7 @@
         <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3150,7 +3135,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>350</v>
+        <v>327</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3164,7 +3149,7 @@
         <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3178,7 +3163,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3192,7 +3177,7 @@
         <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3206,7 +3191,7 @@
         <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3220,7 +3205,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>355</v>
+        <v>277</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3234,7 +3219,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>356</v>
+        <v>274</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3262,7 +3247,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3276,7 +3261,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>356</v>
+        <v>275</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3290,7 +3275,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3304,7 +3289,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3318,7 +3303,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>356</v>
+        <v>271</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3332,7 +3317,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3346,7 +3331,7 @@
         <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3360,7 +3345,7 @@
         <v>259</v>
       </c>
       <c r="D107" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3374,7 +3359,7 @@
         <v>261</v>
       </c>
       <c r="D108" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3388,7 +3373,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>284</v>
+        <v>364</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3402,7 +3387,7 @@
         <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>363</v>
+        <v>334</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3416,7 +3401,7 @@
         <v>262</v>
       </c>
       <c r="D111" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3430,7 +3415,7 @@
         <v>262</v>
       </c>
       <c r="D112" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3444,7 +3429,7 @@
         <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>366</v>
+        <v>334</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3458,7 +3443,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>363</v>
+        <v>288</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3483,7 +3468,7 @@
         <v>259</v>
       </c>
       <c r="C116" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D116" t="s">
         <v>368</v>
@@ -3539,7 +3524,7 @@
         <v>262</v>
       </c>
       <c r="C120" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="D120" t="s">
         <v>372</v>
@@ -3584,7 +3569,7 @@
         <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>284</v>
+        <v>375</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3598,7 +3583,7 @@
         <v>263</v>
       </c>
       <c r="D124" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3612,7 +3597,7 @@
         <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>366</v>
+        <v>377</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3626,7 +3611,7 @@
         <v>262</v>
       </c>
       <c r="D126" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3640,7 +3625,7 @@
         <v>259</v>
       </c>
       <c r="D127" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3654,7 +3639,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3668,7 +3653,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>318</v>
+        <v>381</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3682,7 +3667,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3696,7 +3681,7 @@
         <v>259</v>
       </c>
       <c r="D131" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3710,7 +3695,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3724,7 +3709,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3738,7 +3723,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3752,7 +3737,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3766,7 +3751,7 @@
         <v>263</v>
       </c>
       <c r="D136" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3780,7 +3765,7 @@
         <v>261</v>
       </c>
       <c r="D137" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3794,7 +3779,7 @@
         <v>261</v>
       </c>
       <c r="D138" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3808,7 +3793,7 @@
         <v>261</v>
       </c>
       <c r="D139" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3822,7 +3807,7 @@
         <v>259</v>
       </c>
       <c r="D140" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3836,7 +3821,7 @@
         <v>259</v>
       </c>
       <c r="D141" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3850,7 +3835,7 @@
         <v>261</v>
       </c>
       <c r="D142" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3864,7 +3849,7 @@
         <v>259</v>
       </c>
       <c r="D143" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3878,7 +3863,7 @@
         <v>260</v>
       </c>
       <c r="D144" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3892,7 +3877,7 @@
         <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3906,7 +3891,7 @@
         <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3920,7 +3905,7 @@
         <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -3931,10 +3916,10 @@
         <v>263</v>
       </c>
       <c r="C148" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D148" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -3948,7 +3933,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>396</v>
+        <v>384</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -3962,7 +3947,7 @@
         <v>262</v>
       </c>
       <c r="D150" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -3976,7 +3961,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>398</v>
+        <v>384</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -3990,7 +3975,7 @@
         <v>262</v>
       </c>
       <c r="D152" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -4004,7 +3989,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4018,7 +4003,7 @@
         <v>259</v>
       </c>
       <c r="D154" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4032,7 +4017,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>402</v>
+        <v>274</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4127,7 +4112,7 @@
         <v>262</v>
       </c>
       <c r="C162" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D162" t="s">
         <v>409</v>
@@ -4172,7 +4157,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>412</v>
+        <v>274</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4186,7 +4171,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>413</v>
+        <v>275</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4200,7 +4185,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4214,7 +4199,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>415</v>
+        <v>383</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4228,7 +4213,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>416</v>
+        <v>327</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4242,7 +4227,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>417</v>
+        <v>413</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4256,7 +4241,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>418</v>
+        <v>414</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4270,7 +4255,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>419</v>
+        <v>415</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4284,7 +4269,7 @@
         <v>259</v>
       </c>
       <c r="D173" t="s">
-        <v>420</v>
+        <v>416</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4298,7 +4283,7 @@
         <v>259</v>
       </c>
       <c r="D174" t="s">
-        <v>421</v>
+        <v>417</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4312,7 +4297,7 @@
         <v>259</v>
       </c>
       <c r="D175" t="s">
-        <v>422</v>
+        <v>418</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4323,10 +4308,10 @@
         <v>261</v>
       </c>
       <c r="C176" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D176" t="s">
-        <v>423</v>
+        <v>419</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4340,7 +4325,7 @@
         <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>424</v>
+        <v>420</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4354,7 +4339,7 @@
         <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>425</v>
+        <v>421</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4368,7 +4353,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>426</v>
+        <v>422</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4382,7 +4367,7 @@
         <v>259</v>
       </c>
       <c r="D180" t="s">
-        <v>427</v>
+        <v>423</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4396,7 +4381,7 @@
         <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>428</v>
+        <v>424</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4410,7 +4395,7 @@
         <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>429</v>
+        <v>425</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4424,7 +4409,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>430</v>
+        <v>315</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4438,7 +4423,7 @@
         <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>431</v>
+        <v>426</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4452,7 +4437,7 @@
         <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>432</v>
+        <v>427</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4466,7 +4451,7 @@
         <v>261</v>
       </c>
       <c r="D186" t="s">
-        <v>433</v>
+        <v>428</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4480,7 +4465,7 @@
         <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>434</v>
+        <v>332</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4494,7 +4479,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>430</v>
+        <v>295</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4508,7 +4493,7 @@
         <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>435</v>
+        <v>429</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4522,7 +4507,7 @@
         <v>261</v>
       </c>
       <c r="D190" t="s">
-        <v>436</v>
+        <v>430</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4533,10 +4518,10 @@
         <v>259</v>
       </c>
       <c r="C191" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D191" t="s">
-        <v>437</v>
+        <v>431</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4547,10 +4532,10 @@
         <v>259</v>
       </c>
       <c r="C192" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D192" t="s">
-        <v>438</v>
+        <v>432</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4564,7 +4549,7 @@
         <v>261</v>
       </c>
       <c r="D193" t="s">
-        <v>439</v>
+        <v>433</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4578,7 +4563,7 @@
         <v>261</v>
       </c>
       <c r="D194" t="s">
-        <v>440</v>
+        <v>434</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4592,7 +4577,7 @@
         <v>259</v>
       </c>
       <c r="D195" t="s">
-        <v>441</v>
+        <v>435</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4606,7 +4591,7 @@
         <v>259</v>
       </c>
       <c r="D196" t="s">
-        <v>442</v>
+        <v>436</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4620,7 +4605,7 @@
         <v>261</v>
       </c>
       <c r="D197" t="s">
-        <v>443</v>
+        <v>437</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4634,7 +4619,7 @@
         <v>262</v>
       </c>
       <c r="D198" t="s">
-        <v>444</v>
+        <v>438</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4648,7 +4633,7 @@
         <v>262</v>
       </c>
       <c r="D199" t="s">
-        <v>310</v>
+        <v>439</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4662,7 +4647,7 @@
         <v>259</v>
       </c>
       <c r="D200" t="s">
-        <v>445</v>
+        <v>440</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4676,7 +4661,7 @@
         <v>262</v>
       </c>
       <c r="D201" t="s">
-        <v>446</v>
+        <v>441</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4690,7 +4675,7 @@
         <v>262</v>
       </c>
       <c r="D202" t="s">
-        <v>447</v>
+        <v>442</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4704,7 +4689,7 @@
         <v>259</v>
       </c>
       <c r="D203" t="s">
-        <v>448</v>
+        <v>443</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4715,10 +4700,10 @@
         <v>259</v>
       </c>
       <c r="C204" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D204" t="s">
-        <v>449</v>
+        <v>444</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4732,7 +4717,7 @@
         <v>259</v>
       </c>
       <c r="D205" t="s">
-        <v>450</v>
+        <v>445</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4743,10 +4728,10 @@
         <v>261</v>
       </c>
       <c r="C206" t="s">
-        <v>259</v>
+        <v>266</v>
       </c>
       <c r="D206" t="s">
-        <v>451</v>
+        <v>446</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4757,10 +4742,10 @@
         <v>259</v>
       </c>
       <c r="C207" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D207" t="s">
-        <v>452</v>
+        <v>447</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4774,7 +4759,7 @@
         <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>453</v>
+        <v>448</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4788,7 +4773,7 @@
         <v>261</v>
       </c>
       <c r="D209" t="s">
-        <v>454</v>
+        <v>449</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4802,7 +4787,7 @@
         <v>261</v>
       </c>
       <c r="D210" t="s">
-        <v>455</v>
+        <v>450</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4816,7 +4801,7 @@
         <v>261</v>
       </c>
       <c r="D211" t="s">
-        <v>456</v>
+        <v>451</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4830,7 +4815,7 @@
         <v>261</v>
       </c>
       <c r="D212" t="s">
-        <v>457</v>
+        <v>452</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4844,7 +4829,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>458</v>
+        <v>274</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4858,7 +4843,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>459</v>
+        <v>453</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4872,7 +4857,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>460</v>
+        <v>454</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4886,7 +4871,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>461</v>
+        <v>455</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4900,7 +4885,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>462</v>
+        <v>456</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4914,7 +4899,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>463</v>
+        <v>457</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4928,7 +4913,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>464</v>
+        <v>458</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -4942,7 +4927,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>465</v>
+        <v>459</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -4956,7 +4941,7 @@
         <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>466</v>
+        <v>460</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -4970,7 +4955,7 @@
         <v>261</v>
       </c>
       <c r="D222" t="s">
-        <v>467</v>
+        <v>461</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -4984,7 +4969,7 @@
         <v>259</v>
       </c>
       <c r="D223" t="s">
-        <v>468</v>
+        <v>462</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -4998,7 +4983,7 @@
         <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>469</v>
+        <v>463</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5012,7 +4997,7 @@
         <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>470</v>
+        <v>464</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5026,7 +5011,7 @@
         <v>263</v>
       </c>
       <c r="D226" t="s">
-        <v>471</v>
+        <v>465</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5040,7 +5025,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>430</v>
+        <v>466</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5054,7 +5039,7 @@
         <v>261</v>
       </c>
       <c r="D228" t="s">
-        <v>472</v>
+        <v>467</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5068,7 +5053,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>473</v>
+        <v>466</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5082,7 +5067,7 @@
         <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>474</v>
+        <v>468</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5096,7 +5081,7 @@
         <v>261</v>
       </c>
       <c r="D231" t="s">
-        <v>475</v>
+        <v>469</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5110,7 +5095,7 @@
         <v>259</v>
       </c>
       <c r="D232" t="s">
-        <v>476</v>
+        <v>470</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5124,7 +5109,7 @@
         <v>259</v>
       </c>
       <c r="D233" t="s">
-        <v>477</v>
+        <v>471</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5138,7 +5123,7 @@
         <v>259</v>
       </c>
       <c r="D234" t="s">
-        <v>478</v>
+        <v>472</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5152,7 +5137,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>479</v>
+        <v>473</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5166,7 +5151,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>480</v>
+        <v>474</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5180,7 +5165,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>355</v>
+        <v>278</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5194,7 +5179,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>481</v>
+        <v>475</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5208,7 +5193,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5222,7 +5207,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>482</v>
+        <v>476</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5236,7 +5221,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>483</v>
+        <v>477</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5250,7 +5235,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>484</v>
+        <v>478</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5264,7 +5249,7 @@
         <v>261</v>
       </c>
       <c r="D243" t="s">
-        <v>485</v>
+        <v>479</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5278,7 +5263,7 @@
         <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>486</v>
+        <v>480</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5289,10 +5274,10 @@
         <v>261</v>
       </c>
       <c r="C245" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D245" t="s">
-        <v>487</v>
+        <v>481</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5306,7 +5291,7 @@
         <v>261</v>
       </c>
       <c r="D246" t="s">
-        <v>488</v>
+        <v>482</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5320,7 +5305,7 @@
         <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>489</v>
+        <v>483</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5334,7 +5319,7 @@
         <v>261</v>
       </c>
       <c r="D248" t="s">
-        <v>490</v>
+        <v>484</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5348,7 +5333,7 @@
         <v>261</v>
       </c>
       <c r="D249" t="s">
-        <v>491</v>
+        <v>485</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5362,7 +5347,7 @@
         <v>261</v>
       </c>
       <c r="D250" t="s">
-        <v>492</v>
+        <v>486</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5376,7 +5361,7 @@
         <v>259</v>
       </c>
       <c r="D251" t="s">
-        <v>493</v>
+        <v>487</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5390,7 +5375,7 @@
         <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>494</v>
+        <v>488</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5404,7 +5389,7 @@
         <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>495</v>
+        <v>489</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5418,7 +5403,7 @@
         <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>339</v>
+        <v>490</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5432,7 +5417,7 @@
         <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5446,7 +5431,7 @@
         <v>259</v>
       </c>
       <c r="D256" t="s">
-        <v>496</v>
+        <v>491</v>
       </c>
     </row>
   </sheetData>
